--- a/HNM03S.xlsx
+++ b/HNM03S.xlsx
@@ -3135,7 +3135,7 @@
         <v>15</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -4455,7 +4455,7 @@
         <v>4</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -4775,7 +4775,7 @@
         <v>15</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4795,7 +4795,7 @@
         <v>18</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4855,7 +4855,7 @@
         <v>24</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5135,7 +5135,7 @@
         <v>385</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5175,7 +5175,7 @@
         <v>391</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5195,7 +5195,7 @@
         <v>394</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
